--- a/testCases/Demo_Web_Shop_Test_Cases.xlsx
+++ b/testCases/Demo_Web_Shop_Test_Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,8 @@
 5. Observe the error message.</t>
   </si>
   <si>
-    <t>Email: user@example.comPassword: WrongPassword</t>
+    <t>Email: user@example.com
+Password: WrongPassword</t>
   </si>
   <si>
     <t>An appropriate error message should be displayed and the user should remain on the login page.</t>
@@ -188,7 +189,8 @@
 5. Observe the validation/error message.</t>
   </si>
   <si>
-    <t>Email: user@example.comPassword: Empty</t>
+    <t>Email: user@example.com
+Password: Empty</t>
   </si>
   <si>
     <t>An appropriate validation/error message should be displayed and the user should remain on the login page.</t>
@@ -213,7 +215,8 @@
 5. Observe the validation/error message.</t>
   </si>
   <si>
-    <t>Email: EmptyPassword: WrongPassword</t>
+    <t>Email: Empty
+Password: WrongPassword</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -232,7 +235,8 @@
 5. Observe the validation/error messages.</t>
   </si>
   <si>
-    <t>Email: EmptyPassword: Empty</t>
+    <t>Email: Empty
+Password: Empty</t>
   </si>
   <si>
     <t>Appropriate validation/error message(s) should be displayed and the user should remain on the login page.</t>
@@ -413,7 +417,7 @@
     <t>1. Navigate to Computers → Desktops from side menu or header menu
 2. Click on the Sort By dropdown
 3. Select “Name: A to Z”
-4. Observe the product names displayed</t>
+4. Observe the product names displayed correctly</t>
   </si>
   <si>
     <t>Sort option: Name: A to Z</t>
@@ -437,7 +441,7 @@
     <t>1. Navigate to Computers → Desktops from side menu or header menu
 2. Click on the Sort By dropdown
 3. Select “Name: Z to A”
-4. Observe the product names displayed</t>
+4. Observe the product names displayed correctly</t>
   </si>
   <si>
     <t>Sort option: Name: Z to A</t>
@@ -461,7 +465,7 @@
     <t>1. Navigate to Computers → Desktops from side menu or header menu
 2. Click on the Sort By dropdown
 3. Select “Price: Low to High”
-4. Observe the product prices displayed</t>
+4. Observe the product prices displayed correctly</t>
   </si>
   <si>
     <t>Sort option: Price: Low to High</t>
@@ -485,7 +489,7 @@
     <t>1. Navigate to Computers → Desktops from side menu or header menu
 2. Click on the Sort By dropdown
 3. Select “Price: High to Low”
-4. Observe the product prices displayed</t>
+4. Observe the product prices displayed correctly</t>
   </si>
   <si>
     <t>Sort option: Price: High to Low</t>
@@ -508,18 +512,18 @@
   <si>
     <t>1. Select a featured product.
 2. Add the product to the shopping cart.
-3. Repeat the steps for the required featured products.
+3. Repeat Steps 1–2 for each required featured product.
 4. Verify that the shopping cart count is updated according to the number of products added.
 5. Click Shopping cart.
 6. Verify that the shopping cart page is displayed.
 7. Verify that all selected products are displayed in the cart.
-8. Verify that each product has the correct quantity.</t>
-  </si>
-  <si>
-    <t>Featured products and required quantities</t>
-  </si>
-  <si>
-    <t>All selected featured products should be added successfully to the shopping cart. The cart count should match the number of products added, and each selected product should be displayed with the correct quantity.</t>
+8. Verify that each product has the correct quantity and name.</t>
+  </si>
+  <si>
+    <t>Featured products</t>
+  </si>
+  <si>
+    <t>All selected featured products should be added successfully to the shopping cart. The cart count should match the number of products added, and each selected product should be displayed with the correct quantity and name.</t>
   </si>
   <si>
     <t>All selected featured products were added successfully. The cart count matched the number of products added, and the products were displayed with the correct quantities.</t>
